--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-09-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-09-2025.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>£10.87</t>
+          <t>£10.76</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>£12.01</t>
+          <t>£11.89</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>£15.59</t>
+          <t>£15.43</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>£15.91</t>
+          <t>£15.75</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>£20.39</t>
+          <t>£20.19</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>£22.02</t>
+          <t>£21.80</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>£22.34</t>
+          <t>£22.12</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>£25.53</t>
+          <t>£25.27</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>£27.67</t>
+          <t>£27.39</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>£27.18</t>
+          <t>£26.91</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>£33.38</t>
+          <t>£33.05</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>£40.69</t>
+          <t>£40.28</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>£41.51</t>
+          <t>£41.09</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>£41.44</t>
+          <t>£41.03</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>£709.65</t>
+          <t>£702.55</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>£890.89</t>
+          <t>£881.98</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>£28.99</t>
+          <t>£28.70</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>£35.00</t>
+          <t>£34.65</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>£38.00</t>
+          <t>£37.62</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>£43.31</t>
+          <t>£42.88</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>£43.99</t>
+          <t>£43.55</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 520 Server Error: &lt;none&gt; for url: https://www.humancapitalconsultants.com/</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>£47.51</t>
+          <t>£47.03</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 520 Server Error: &lt;none&gt; for url: https://www.windwarrior.com/about-honor/</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>£43.58</t>
+          <t>£43.14</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 522 Server Error: &lt;none&gt; for url: https://imperialhouse-nj.com/contact-us-2/</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>£1140.48</t>
+          <t>£1129.12</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>£1267.2</t>
+          <t>£1254.56</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>£1201.12</t>
+          <t>£1189.12</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
